--- a/data/trans_orig/P1435_2011_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1435_2011_2023-Provincia-trans_orig.xlsx
@@ -731,7 +731,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>289633</t>
+          <t>290035</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>275510</t>
+          <t>274529</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>285179</t>
+          <t>285162</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>569199</t>
+          <t>568173</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>579863</t>
+          <t>579844</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5105</t>
+          <t>4703</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>2083</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11735</t>
+          <t>12716</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>2139</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12784</t>
+          <t>13810</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>494550</t>
+          <t>495062</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>504465</t>
+          <t>504472</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>489153</t>
+          <t>489241</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>510671</t>
+          <t>509332</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>989836</t>
+          <t>990650</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1012529</t>
+          <t>1012839</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10977</t>
+          <t>10465</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13094</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34612</t>
+          <t>34524</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>16763</t>
+          <t>16453</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>39456</t>
+          <t>38642</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -1678,12 +1678,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>317687</t>
+          <t>318612</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>334208</t>
+          <t>334834</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>641429</t>
+          <t>641919</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>658267</t>
+          <t>658962</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -1791,12 +1791,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6812</t>
+          <t>6186</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23333</t>
+          <t>22408</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6799</t>
+          <t>6104</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23637</t>
+          <t>23147</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,12 +1841,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>365327</t>
+          <t>366044</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>373063</t>
+          <t>373066</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,12 +2114,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>354010</t>
+          <t>355219</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>373591</t>
+          <t>373545</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>726420</t>
+          <t>726308</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>745642</t>
+          <t>745677</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,12 +2184,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,74%</t>
         </is>
       </c>
     </row>
@@ -2212,12 +2212,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>916</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8655</t>
+          <t>7938</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,12 +2227,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15360</t>
+          <t>15406</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34941</t>
+          <t>33732</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17291</t>
+          <t>17256</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>36513</t>
+          <t>36625</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -2590,12 +2590,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>201195</t>
+          <t>201018</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>214282</t>
+          <t>214409</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2625,12 +2625,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>414133</t>
+          <t>413644</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>427072</t>
+          <t>427046</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2703,12 +2703,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18396</t>
+          <t>18573</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2738,12 +2738,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>5137</t>
+          <t>5163</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>18076</t>
+          <t>18565</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>268722</t>
+          <t>268553</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3046,12 +3046,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>264451</t>
+          <t>264262</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>275994</t>
+          <t>275979</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>536544</t>
+          <t>536505</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>549463</t>
+          <t>549024</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3096,12 +3096,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5428</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3159,12 +3159,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4037</t>
+          <t>4052</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15580</t>
+          <t>15769</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3194,12 +3194,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>4988</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17468</t>
+          <t>17507</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3209,12 +3209,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -3467,7 +3467,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>655523</t>
+          <t>656631</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3502,12 +3502,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>654206</t>
+          <t>652169</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>674859</t>
+          <t>675090</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3517,12 +3517,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1312725</t>
+          <t>1314369</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1337044</t>
+          <t>1336649</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7265</t>
+          <t>6157</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3615,12 +3615,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>18994</t>
+          <t>18763</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>39647</t>
+          <t>41684</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3630,12 +3630,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>19597</t>
+          <t>19992</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>43916</t>
+          <t>42272</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>796329</t>
+          <t>793604</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>814184</t>
+          <t>813249</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1575029</t>
+          <t>1574852</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1593212</t>
+          <t>1593089</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>9669</t>
+          <t>10604</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>27524</t>
+          <t>30249</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>9739</t>
+          <t>9862</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>27922</t>
+          <t>28099</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3407438</t>
+          <t>3407724</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3420946</t>
+          <t>3420866</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3407965</t>
+          <t>3406722</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3453096</t>
+          <t>3451374</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>6823216</t>
+          <t>6822437</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6870768</t>
+          <t>6870771</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>5833</t>
+          <t>5913</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>19341</t>
+          <t>19055</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>105213</t>
+          <t>106935</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>150344</t>
+          <t>151587</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>114320</t>
+          <t>114317</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>161872</t>
+          <t>162651</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -5179,32 +5179,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6806</t>
+          <t>5854</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2690</t>
+          <t>2159</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15453</t>
+          <t>12958</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5214,32 +5214,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19992</t>
+          <t>19384</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13650</t>
+          <t>13756</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28871</t>
+          <t>27720</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5249,32 +5249,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>26799</t>
+          <t>25238</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19023</t>
+          <t>18217</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38662</t>
+          <t>35571</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -5292,32 +5292,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>304637</t>
+          <t>312991</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>295990</t>
+          <t>305887</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>308753</t>
+          <t>316686</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5327,32 +5327,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>269643</t>
+          <t>296677</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>260764</t>
+          <t>288341</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>275985</t>
+          <t>302305</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5362,32 +5362,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>574278</t>
+          <t>609668</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>562415</t>
+          <t>599335</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>582054</t>
+          <t>616689</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>
@@ -5405,17 +5405,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5440,17 +5440,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5475,17 +5475,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5635,32 +5635,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5877</t>
+          <t>6090</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2271</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13717</t>
+          <t>13598</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5670,67 +5670,67 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36416</t>
+          <t>36721</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27424</t>
+          <t>28155</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48511</t>
+          <t>49332</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
+          <t>5,16%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>9,04%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>42812</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>32344</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>57374</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>3,98%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
           <t>5,33%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>9,43%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>42293</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>32500</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>54923</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>4,1%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>3,15%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -5748,32 +5748,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>511516</t>
+          <t>523570</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>503676</t>
+          <t>516062</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>515122</t>
+          <t>527829</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5783,67 +5783,67 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>477875</t>
+          <t>509088</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>465780</t>
+          <t>496477</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>486867</t>
+          <t>517654</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
+          <t>94,84%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1042</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1032657</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>1018095</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>1043125</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>96,02%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>94,67%</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1042</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>989391</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>976761</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>999184</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>95,9%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>94,68%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,99%</t>
         </is>
       </c>
     </row>
@@ -5861,17 +5861,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5896,17 +5896,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>514291</t>
+          <t>545809</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>514291</t>
+          <t>545809</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>514291</t>
+          <t>545809</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5931,17 +5931,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1031684</t>
+          <t>1075469</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1031684</t>
+          <t>1075469</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1031684</t>
+          <t>1075469</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6091,32 +6091,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5113</t>
+          <t>5838</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2281</t>
+          <t>2776</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10144</t>
+          <t>11158</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6126,32 +6126,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>26470</t>
+          <t>26742</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19414</t>
+          <t>19917</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35382</t>
+          <t>35557</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6161,32 +6161,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>31583</t>
+          <t>32580</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23401</t>
+          <t>24941</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41240</t>
+          <t>42858</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -6204,32 +6204,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>310937</t>
+          <t>310155</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>305906</t>
+          <t>304835</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>313769</t>
+          <t>313217</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6239,32 +6239,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>322658</t>
+          <t>329639</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>313746</t>
+          <t>320824</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>329714</t>
+          <t>336464</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6274,32 +6274,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>633595</t>
+          <t>639795</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>623938</t>
+          <t>629517</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>641777</t>
+          <t>647434</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,29%</t>
         </is>
       </c>
     </row>
@@ -6317,17 +6317,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6352,17 +6352,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6387,17 +6387,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1175</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3512</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6582,32 +6582,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>31950</t>
+          <t>33766</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19598</t>
+          <t>24812</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>45047</t>
+          <t>43496</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6617,27 +6617,27 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>33115</t>
+          <t>34942</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23080</t>
+          <t>25938</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45080</t>
+          <t>45468</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6660,27 +6660,27 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>311392</t>
+          <t>371970</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>309045</t>
+          <t>369025</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -6695,32 +6695,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>443768</t>
+          <t>388195</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>430671</t>
+          <t>378465</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>456120</t>
+          <t>397149</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6730,22 +6730,22 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>755159</t>
+          <t>760165</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>743194</t>
+          <t>749639</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>765194</t>
+          <t>769169</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,74%</t>
         </is>
       </c>
     </row>
@@ -6773,17 +6773,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6808,17 +6808,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6843,17 +6843,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7003,32 +7003,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3703</t>
+          <t>3728</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1149</t>
+          <t>731</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11190</t>
+          <t>9795</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7038,32 +7038,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>16136</t>
+          <t>17608</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11826</t>
+          <t>12233</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>21902</t>
+          <t>23084</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7073,32 +7073,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>19838</t>
+          <t>21335</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>14034</t>
+          <t>15071</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>27818</t>
+          <t>29515</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -7116,32 +7116,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>175039</t>
+          <t>201937</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>167552</t>
+          <t>195870</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>177593</t>
+          <t>204934</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7151,32 +7151,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>191780</t>
+          <t>208837</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>186014</t>
+          <t>203361</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>196090</t>
+          <t>214212</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7186,32 +7186,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>366820</t>
+          <t>410774</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>358840</t>
+          <t>402594</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>372624</t>
+          <t>417038</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,51%</t>
         </is>
       </c>
     </row>
@@ -7229,17 +7229,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7264,17 +7264,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>207916</t>
+          <t>226445</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>207916</t>
+          <t>226445</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>207916</t>
+          <t>226445</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7299,17 +7299,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>386658</t>
+          <t>432109</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>386658</t>
+          <t>432109</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>386658</t>
+          <t>432109</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7459,32 +7459,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3476</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7838</t>
+          <t>7540</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7494,32 +7494,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>27473</t>
+          <t>28324</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>21078</t>
+          <t>22113</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>34922</t>
+          <t>36348</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7529,32 +7529,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>30948</t>
+          <t>31724</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>23601</t>
+          <t>24513</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>39383</t>
+          <t>41198</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -7572,32 +7572,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>266160</t>
+          <t>267307</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>261798</t>
+          <t>263167</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>268296</t>
+          <t>269415</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7607,32 +7607,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>228914</t>
+          <t>234775</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>221465</t>
+          <t>226751</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>235309</t>
+          <t>240986</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7642,32 +7642,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>495075</t>
+          <t>502082</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>486640</t>
+          <t>492608</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>502422</t>
+          <t>509293</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,41%</t>
         </is>
       </c>
     </row>
@@ -7685,17 +7685,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7720,17 +7720,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7755,17 +7755,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7915,32 +7915,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>17772</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9147</t>
+          <t>9824</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>30387</t>
+          <t>30985</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7950,32 +7950,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>287346</t>
+          <t>105996</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>102221</t>
+          <t>89410</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>569208</t>
+          <t>124252</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7985,32 +7985,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>303810</t>
+          <t>123767</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>109607</t>
+          <t>104731</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>728483</t>
+          <t>146761</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -8028,32 +8028,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>606021</t>
+          <t>699949</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>592098</t>
+          <t>686736</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>613338</t>
+          <t>707897</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8063,32 +8063,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>560320</t>
+          <t>663245</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>278458</t>
+          <t>644989</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>745445</t>
+          <t>679831</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8098,32 +8098,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1166341</t>
+          <t>1363195</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>741668</t>
+          <t>1340201</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1360544</t>
+          <t>1382231</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,96%</t>
         </is>
       </c>
     </row>
@@ -8141,17 +8141,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>622485</t>
+          <t>717721</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>622485</t>
+          <t>717721</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>622485</t>
+          <t>717721</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8176,17 +8176,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>847666</t>
+          <t>769241</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>847666</t>
+          <t>769241</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>847666</t>
+          <t>769241</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8211,17 +8211,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1470151</t>
+          <t>1486962</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1470151</t>
+          <t>1486962</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1470151</t>
+          <t>1486962</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8371,32 +8371,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>13974</t>
+          <t>15718</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>9493</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>24594</t>
+          <t>27093</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8406,32 +8406,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>61786</t>
+          <t>65199</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>49842</t>
+          <t>51133</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>79834</t>
+          <t>78235</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8441,32 +8441,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>75760</t>
+          <t>80916</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>45586</t>
+          <t>67059</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>98733</t>
+          <t>97182</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -8484,32 +8484,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>914746</t>
+          <t>782354</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>904126</t>
+          <t>770979</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>923521</t>
+          <t>788579</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8519,32 +8519,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>652868</t>
+          <t>764599</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>634820</t>
+          <t>751563</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>664812</t>
+          <t>778665</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8554,32 +8554,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1567614</t>
+          <t>1546954</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1544641</t>
+          <t>1530688</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1597788</t>
+          <t>1560811</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>95,88%</t>
         </is>
       </c>
     </row>
@@ -8597,17 +8597,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8632,17 +8632,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>714654</t>
+          <t>829798</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>714654</t>
+          <t>829798</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>714654</t>
+          <t>829798</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8667,17 +8667,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>1643374</t>
+          <t>1627870</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1643374</t>
+          <t>1627870</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1643374</t>
+          <t>1627870</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8827,27 +8827,27 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>56578</t>
+          <t>59574</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>39830</t>
+          <t>44605</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>75382</t>
+          <t>76856</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -8862,32 +8862,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>507569</t>
+          <t>333739</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>310448</t>
+          <t>307501</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1046860</t>
+          <t>364220</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8897,32 +8897,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>564146</t>
+          <t>393314</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>358827</t>
+          <t>358755</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1338126</t>
+          <t>430079</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -8940,22 +8940,22 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3400448</t>
+          <t>3470234</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3381644</t>
+          <t>3452952</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3417196</t>
+          <t>3485203</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -8965,7 +8965,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8975,32 +8975,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>3147824</t>
+          <t>3395057</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2608533</t>
+          <t>3364576</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3344945</t>
+          <t>3421295</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9010,32 +9010,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>6548273</t>
+          <t>6865290</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>5774293</t>
+          <t>6828525</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6753592</t>
+          <t>6899849</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,06%</t>
         </is>
       </c>
     </row>
@@ -9053,17 +9053,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>3457026</t>
+          <t>3529808</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>3457026</t>
+          <t>3529808</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>3457026</t>
+          <t>3529808</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -9088,17 +9088,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>3655393</t>
+          <t>3728796</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>3655393</t>
+          <t>3728796</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3655393</t>
+          <t>3728796</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -9123,17 +9123,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>7112419</t>
+          <t>7258604</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>7112419</t>
+          <t>7258604</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>7112419</t>
+          <t>7258604</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
